--- a/data_out/country_spreadsheets/Bulgaria.xlsx
+++ b/data_out/country_spreadsheets/Bulgaria.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W29"/>
+  <dimension ref="A1:AN29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,87 +461,172 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Median drought days per year</t>
+          <t>Median drought-warning-days</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Maximum recorded drought days per year</t>
+          <t>Maximum recorded drought-warning-days</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>most severe drought year</t>
+          <t>Year of maximum drought-warning-days</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2012</t>
+          <t>Warning days 2012</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2013</t>
+          <t>Warning days 2013</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2014</t>
+          <t>Warning days 2014</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2015</t>
+          <t>Warning days 2015</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2016</t>
+          <t>Warning days 2016</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2017</t>
+          <t>Warning days 2017</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2018</t>
+          <t>Warning days 2018</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2019</t>
+          <t>Warning days 2019</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2020</t>
+          <t>Warning days 2020</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2021</t>
+          <t>Warning days 2021</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2022</t>
+          <t>Warning days 2022</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2023</t>
+          <t>Warning days 2023</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2024</t>
+          <t>Warning days 2024</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2025</t>
+          <t>Warning days 2025</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Median drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Maximum recorded drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Year of maximum drought-alert-days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2012</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2013</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2014</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2015</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2016</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2017</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2018</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2019</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2020</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2021</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2022</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2023</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2024</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2025</t>
         </is>
       </c>
     </row>
@@ -621,6 +706,57 @@
       <c r="W2" t="n">
         <v>239.71</v>
       </c>
+      <c r="X2" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>81.72</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>293.63</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>204.46</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>38.83</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>106.07</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>89.11</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>201.72</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>56.26</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>130.47</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>44.07</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>177.2</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>239.71</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -698,6 +834,57 @@
       <c r="W3" t="n">
         <v>233.91</v>
       </c>
+      <c r="X3" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>66.58</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>239.87</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>275.96</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>96.25</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>47.08</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>66.11</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>173.13</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>149.85</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>91.39</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>50.17</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>223.59</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>233.91</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -775,6 +962,57 @@
       <c r="W4" t="n">
         <v>241.1</v>
       </c>
+      <c r="X4" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>69.73999999999999</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>157.03</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>217.58</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>96.89</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>32.66</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>47.04</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>172.03</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>170.36</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>27.46</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>79.73</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>236.19</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>241.1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -852,6 +1090,57 @@
       <c r="W5" t="n">
         <v>167.53</v>
       </c>
+      <c r="X5" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>67.05</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>179.95</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>170.71</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>41.06</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>100.81</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>190.33</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>27.72</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>180.06</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>102.28</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>254.76</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>167.53</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -929,6 +1218,57 @@
       <c r="W6" t="n">
         <v>170.57</v>
       </c>
+      <c r="X6" t="n">
+        <v>19.96</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>60.44</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>178.35</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>107.58</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>89.98999999999999</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>48.64</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>22.11</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>125.56</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>142.63</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>31.62</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>152.57</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>116.52</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>247.07</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>170.57</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1006,6 +1346,57 @@
       <c r="W7" t="n">
         <v>166.18</v>
       </c>
+      <c r="X7" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>72.41</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>137.04</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>34.71</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>13.24</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>61.85</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>64.72</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>179.92</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>276.43</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>33.07</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>228.02</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>294.4</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>333.01</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>166.18</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1083,6 +1474,57 @@
       <c r="W8" t="n">
         <v>156.18</v>
       </c>
+      <c r="X8" t="n">
+        <v>25.33</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>72.66</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>145.66</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>45.12</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>63.57</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>61.94</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>38.24</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>141.9</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>226.19</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>192.84</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>181.96</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>274.56</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>156.18</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1160,6 +1602,57 @@
       <c r="W9" t="n">
         <v>84.7</v>
       </c>
+      <c r="X9" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>71.48999999999999</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>190.83</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>32.85</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>87.88</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>244.39</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>17.13</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>146.69</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>189.68</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>266.27</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>84.7</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1237,6 +1730,57 @@
       <c r="W10" t="n">
         <v>133.42</v>
       </c>
+      <c r="X10" t="n">
+        <v>16.39</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>57.95</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>83.52</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>270.18</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>26.68</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>121.28</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>193.41</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>232.19</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>133.42</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1314,6 +1858,57 @@
       <c r="W11" t="n">
         <v>103.63</v>
       </c>
+      <c r="X11" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>73.88</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>38.61</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>62.87</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>296.43</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>207.08</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>289.53</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>172.12</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>103.63</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1391,6 +1986,57 @@
       <c r="W12" t="n">
         <v>206.36</v>
       </c>
+      <c r="X12" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>68.11</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2023</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>102.69</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>65.06</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>23.48</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>147.66</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>260.11</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>93.06999999999999</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>288.91</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>130.05</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>206.36</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1468,6 +2114,57 @@
       <c r="W13" t="n">
         <v>103.5</v>
       </c>
+      <c r="X13" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>47.82</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>92.38</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>71.31</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>27.55</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>174.76</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>260.05</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>93.54000000000001</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>300.34</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>134.31</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>103.5</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1545,6 +2242,57 @@
       <c r="W14" t="n">
         <v>197.84</v>
       </c>
+      <c r="X14" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>68.45</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>71.44</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>15.86</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>20.54</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>57.84</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>127.14</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>287.13</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>19.61</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>134.48</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>271.57</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>260.29</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>197.84</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1622,6 +2370,57 @@
       <c r="W15" t="n">
         <v>172.5</v>
       </c>
+      <c r="X15" t="n">
+        <v>19.56</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>78.77</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>12.52</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>59.59</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>138.67</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>293.53</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>140.45</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>236.25</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>272.26</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>172.5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1699,6 +2498,57 @@
       <c r="W16" t="n">
         <v>153.21</v>
       </c>
+      <c r="X16" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>43.04</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2023</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>52.02</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>53.71</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>134.83</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>63.77</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>117.66</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>19.39</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>236.47</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>22.01</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>85.48</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>263.01</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>158.24</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>153.21</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1776,6 +2626,57 @@
       <c r="W17" t="n">
         <v>142.25</v>
       </c>
+      <c r="X17" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>61.02</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>85.84</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>93.76000000000001</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>22.64</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>102.14</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>19.24</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>294.26</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>24.56</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>132.89</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>332.64</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>295.13</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>142.25</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1853,6 +2754,57 @@
       <c r="W18" t="n">
         <v>208.21</v>
       </c>
+      <c r="X18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>41.23</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>64.95</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>42.01</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>72.84</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>24.08</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>82.16</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>323.68</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>26.91</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>120.19</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>340.45</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>310.07</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>208.21</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1930,6 +2882,57 @@
       <c r="W19" t="n">
         <v>191</v>
       </c>
+      <c r="X19" t="n">
+        <v>19.14</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>59.44</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>132.38</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>77.69</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>51.06</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>190.14</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>232.31</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>182.35</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>280.38</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>318.75</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>191</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -2007,6 +3010,57 @@
       <c r="W20" t="n">
         <v>226.46</v>
       </c>
+      <c r="X20" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>40.85</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>196.14</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>174.01</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>42.48</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>30.12</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>17.61</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>140.25</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>78.97</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>28.24</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>43.83</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>200.96</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>226.46</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -2084,6 +3138,57 @@
       <c r="W21" t="n">
         <v>230.92</v>
       </c>
+      <c r="X21" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>149.17</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>163.08</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>112.04</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>52.95</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>40.55</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>164.79</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>72.42</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>35.94</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>65.48</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>222.48</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>230.92</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -2161,6 +3266,57 @@
       <c r="W22" t="n">
         <v>247.08</v>
       </c>
+      <c r="X22" t="n">
+        <v>12.41</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>131.75</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>71.20999999999999</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>86.64</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>171.62</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>84.31999999999999</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>218.34</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>51.92</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>55.19</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>70.65000000000001</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>86.86</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>234.04</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>247.08</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -2238,6 +3394,57 @@
       <c r="W23" t="n">
         <v>122.79</v>
       </c>
+      <c r="X23" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>47.87</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>246.47</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>209.69</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>84.56</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>69.27</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>32.84</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>156.16</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>52.38</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>19.07</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>39.32</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>108.87</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>122.79</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -2315,6 +3522,57 @@
       <c r="W24" t="n">
         <v>195.07</v>
       </c>
+      <c r="X24" t="n">
+        <v>15.76</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>243.02</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>112.47</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>88.64</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>24.34</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>149.24</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>230.57</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>119.67</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>38.05</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>44.19</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>42.65</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>146.75</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>195.07</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -2392,6 +3650,57 @@
       <c r="W25" t="n">
         <v>171.01</v>
       </c>
+      <c r="X25" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>55.64</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>130.6</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>103.04</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>60.47</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>65.48999999999999</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>69.70999999999999</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>123.66</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>97.38</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>218.85</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>171.01</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -2469,6 +3778,57 @@
       <c r="W26" t="n">
         <v>250.61</v>
       </c>
+      <c r="X26" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>63.84</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>86.44</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>72.26000000000001</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>70.56999999999999</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>159.34</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>28.39</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>145.95</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>145</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>187.7</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>328.5</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>250.61</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -2546,6 +3906,57 @@
       <c r="W27" t="n">
         <v>265.53</v>
       </c>
+      <c r="X27" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>55.06</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>186.09</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>218.65</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>130.91</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>32.93</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>62.97</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>165.3</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>68.23999999999999</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>32.34</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>87.42</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>261.3</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>265.53</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -2623,6 +4034,57 @@
       <c r="W28" t="n">
         <v>224.11</v>
       </c>
+      <c r="X28" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>68.48</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2016</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>97.63</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>182.24</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>30.02</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>30.85</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>93.27</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>129.48</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>277.98</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>224.11</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -2698,6 +4160,57 @@
         <v>311.2</v>
       </c>
       <c r="W29" t="n">
+        <v>229.1</v>
+      </c>
+      <c r="X29" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>66.65000000000001</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>65.08</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>22.71</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>109.37</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>74.26000000000001</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>189.15</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>138.91</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>311.2</v>
+      </c>
+      <c r="AN29" t="n">
         <v>229.1</v>
       </c>
     </row>
